--- a/output/pdf_financials_xlsx/CFY.xlsx
+++ b/output/pdf_financials_xlsx/CFY.xlsx
@@ -1093,7 +1093,7 @@
         <v>-0.005974</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>0.016152</v>
+        <v>-0.016152</v>
       </c>
       <c r="M16" s="1" t="inlineStr">
         <is>
@@ -1327,7 +1327,7 @@
         <v>-0.005974</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>0.016152</v>
+        <v>-0.016152</v>
       </c>
       <c r="M20" s="1" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>-0.005974</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>0.016152</v>
+        <v>-0.016152</v>
       </c>
       <c r="M23" s="1" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>-0.005974</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>0.016152</v>
+        <v>-0.016152</v>
       </c>
       <c r="M27" s="1" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
         <v>-0.004305</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>0.017996</v>
+        <v>-0.014308</v>
       </c>
       <c r="M29" s="1" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
         <v>-0.9919583400539183</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>3.4609356219049</v>
+        <v>-2.751670753401606</v>
       </c>
       <c r="M30" s="1" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         <v>-0</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M31" s="1" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         <v>-1.376529413120118</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>3.106303187653253</v>
+        <v>-3.106303187653253</v>
       </c>
       <c r="M32" s="1" t="inlineStr">
         <is>
@@ -4622,7 +4622,7 @@
         <v>3.971706</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0</v>
+        <v>3.971706</v>
       </c>
       <c r="E91" s="3" t="n">
         <v>0</v>
@@ -4996,7 +4996,7 @@
         <v>-0.005974</v>
       </c>
       <c r="L99" s="3" t="n">
-        <v>0.016152</v>
+        <v>-0.016152</v>
       </c>
       <c r="M99" s="1" t="inlineStr">
         <is>
@@ -21888,7 +21888,11 @@
           <t>Exchange translation reserve 8,410,072</t>
         </is>
       </c>
-      <c r="D201" t="inlineStr"/>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E201" t="inlineStr">
         <is>
           <t>-</t>
@@ -28556,7 +28560,7 @@
         <v>-0.005974</v>
       </c>
       <c r="O292" s="5" t="n">
-        <v>0.016152</v>
+        <v>-0.016152</v>
       </c>
       <c r="P292" t="inlineStr">
         <is>
@@ -48974,7 +48978,7 @@
         <v>-0.005974</v>
       </c>
       <c r="O563" s="5" t="n">
-        <v>0.016152</v>
+        <v>-0.016152</v>
       </c>
       <c r="P563" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/CFY.xlsx
+++ b/output/pdf_financials_xlsx/CFY.xlsx
@@ -879,10 +879,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.036892</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.256776</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -1686,10 +1686,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>5.407785</v>
+        <v>5.444677</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>8.018055</v>
+        <v>8.274831000000001</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>8.018055</v>
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>5.407785</v>
+        <v>5.444677</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>8.018055</v>
+        <v>8.274831000000001</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>8.023816999999999</v>
@@ -1843,10 +1843,10 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>12.86066191140958</v>
+        <v>12.94839756274109</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>15.09190261923462</v>
+        <v>15.57521663827747</v>
       </c>
       <c r="D30" s="3" t="n">
         <v>2626.926942657434</v>
@@ -2021,10 +2021,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>15.15143</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>12.11998</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>0</v>
@@ -2107,10 +2107,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>15.15143</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>12.11998</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>0</v>
@@ -2623,10 +2623,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>16.148521</v>
+        <v>0.9970909999999999</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>13.068792</v>
+        <v>0.948812</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>20.168667</v>
@@ -22290,7 +22290,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E206" s="5" t="n">
@@ -57540,7 +57540,7 @@
       </c>
       <c r="D677" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E677" s="5" t="n">

--- a/output/pdf_financials_xlsx/CFY.xlsx
+++ b/output/pdf_financials_xlsx/CFY.xlsx
@@ -1749,34 +1749,34 @@
         <v>0</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0.005762</v>
+        <v>0.021786</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0.000139</v>
+        <v>0.017071</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0.000456</v>
+        <v>0.018434</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.000568</v>
+        <v>0.019357</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0.000625</v>
+        <v>0.021073</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0.001223</v>
+        <v>0.029993</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0.001526</v>
+        <v>0.037276</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0.001669</v>
+        <v>0.039964</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0.001844</v>
+        <v>0.042239</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>0.001928</v>
+        <v>0.043725</v>
       </c>
     </row>
     <row r="29">
@@ -1792,7 +1792,7 @@
         <v>8.274831000000001</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>8.023816999999999</v>
+        <v>8.039840999999999</v>
       </c>
       <c r="E29" s="1" t="inlineStr">
         <is>
@@ -1825,10 +1825,10 @@
         </is>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.004305</v>
+        <v>0.03399</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.014308</v>
+        <v>0.026087</v>
       </c>
       <c r="M29" s="1" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>15.57521663827747</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>2626.926942657434</v>
+        <v>2632.173058979522</v>
       </c>
       <c r="E30" s="1" t="inlineStr">
         <is>
@@ -1882,10 +1882,10 @@
         </is>
       </c>
       <c r="K30" s="3" t="n">
-        <v>-0.9919583400539183</v>
+        <v>7.831977695338602</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>-2.751670753401606</v>
+        <v>5.01697196980624</v>
       </c>
       <c r="M30" s="1" t="inlineStr">
         <is>
@@ -5017,34 +5017,34 @@
         <v>0</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.021786</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>0.017071</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>0.018434</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>0.019357</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>0.021073</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>0.029993</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>0.037276</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>0.039964</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>0.042239</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>0.043725</v>
       </c>
     </row>
     <row r="101">
@@ -5533,13 +5533,13 @@
         <v>0</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0</v>
+        <v>9e-06</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>4.5e-05</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>0</v>
+        <v>0.000895</v>
       </c>
       <c r="G112" s="3" t="n">
         <v>0</v>
@@ -5548,19 +5548,19 @@
         <v>0</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>0</v>
+        <v>0.001006</v>
       </c>
       <c r="J112" s="3" t="n">
-        <v>0</v>
+        <v>0.003211</v>
       </c>
       <c r="K112" s="3" t="n">
-        <v>0</v>
+        <v>0.00013</v>
       </c>
       <c r="L112" s="3" t="n">
-        <v>0</v>
+        <v>0.000655</v>
       </c>
       <c r="M112" s="3" t="n">
-        <v>0</v>
+        <v>2.3e-05</v>
       </c>
     </row>
     <row r="113">
@@ -25172,7 +25172,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D244" t="inlineStr"/>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E244" t="inlineStr">
         <is>
           <t>-</t>
@@ -25230,7 +25234,11 @@
           <t>Depreciation of right-of-use assets</t>
         </is>
       </c>
-      <c r="D245" t="inlineStr"/>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E245" t="inlineStr">
         <is>
           <t>-</t>
@@ -25362,7 +25370,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -27334,7 +27342,11 @@
           <t>Proceeds on disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D275" t="inlineStr"/>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E275" t="inlineStr">
         <is>
           <t>-</t>
@@ -36098,7 +36110,7 @@
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
@@ -37820,7 +37832,11 @@
           <t>Proceeds from disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D416" t="inlineStr"/>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E416" t="inlineStr">
         <is>
           <t>-</t>
@@ -38868,7 +38884,7 @@
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E430" t="inlineStr">
@@ -40592,7 +40608,11 @@
           <t>Loss on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D453" t="inlineStr"/>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E453" t="inlineStr">
         <is>
           <t>-</t>
@@ -41950,7 +41970,11 @@
           <t>Depreciation of property and equipment 3,110,178</t>
         </is>
       </c>
-      <c r="D471" t="inlineStr"/>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E471" t="inlineStr">
         <is>
           <t>-</t>
@@ -42104,7 +42128,7 @@
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E473" t="inlineStr">

--- a/output/pdf_financials_xlsx/CFY.xlsx
+++ b/output/pdf_financials_xlsx/CFY.xlsx
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0</v>
+        <v>4.966195</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0</v>
+        <v>-2.684344</v>
       </c>
       <c r="D106" s="3" t="n">
         <v>-1.902864</v>
@@ -5324,7 +5324,7 @@
         <v>0</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>0</v>
+        <v>0.004485</v>
       </c>
       <c r="G107" s="3" t="n">
         <v>0.003326</v>
@@ -5333,10 +5333,10 @@
         <v>-0.003326</v>
       </c>
       <c r="I107" s="3" t="n">
-        <v>0</v>
+        <v>0.000781</v>
       </c>
       <c r="J107" s="3" t="n">
-        <v>0</v>
+        <v>-0.000781</v>
       </c>
       <c r="K107" s="3" t="n">
         <v>0</v>
@@ -5699,40 +5699,40 @@
         </is>
       </c>
       <c r="B116" s="3" t="n">
-        <v>0</v>
+        <v>-0.822581</v>
       </c>
       <c r="C116" s="3" t="n">
-        <v>0</v>
+        <v>-0.008812</v>
       </c>
       <c r="D116" s="3" t="n">
-        <v>0</v>
+        <v>-8.000000000000001e-05</v>
       </c>
       <c r="E116" s="3" t="n">
-        <v>0</v>
+        <v>-0.001701</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>0</v>
+        <v>-0.001509</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>0</v>
+        <v>-0.000549</v>
       </c>
       <c r="H116" s="3" t="n">
-        <v>0</v>
+        <v>-0.001833</v>
       </c>
       <c r="I116" s="3" t="n">
-        <v>0</v>
+        <v>-0.000225</v>
       </c>
       <c r="J116" s="3" t="n">
-        <v>0</v>
+        <v>-0.002192</v>
       </c>
       <c r="K116" s="3" t="n">
-        <v>0</v>
+        <v>-0.001664</v>
       </c>
       <c r="L116" s="3" t="n">
-        <v>0</v>
+        <v>-0.001131</v>
       </c>
       <c r="M116" s="3" t="n">
-        <v>0</v>
+        <v>-0.0006579999999999999</v>
       </c>
     </row>
     <row r="117">
@@ -5934,16 +5934,16 @@
         </is>
       </c>
       <c r="B121" s="3" t="n">
-        <v>0</v>
+        <v>-0.537019</v>
       </c>
       <c r="C121" s="3" t="n">
-        <v>0</v>
+        <v>-0.598782</v>
       </c>
       <c r="D121" s="3" t="n">
-        <v>0</v>
+        <v>-0.002002</v>
       </c>
       <c r="E121" s="3" t="n">
-        <v>0</v>
+        <v>-0.001086</v>
       </c>
       <c r="F121" s="3" t="n">
         <v>0</v>
@@ -5955,7 +5955,7 @@
         <v>0</v>
       </c>
       <c r="I121" s="3" t="n">
-        <v>0</v>
+        <v>-0.000225</v>
       </c>
       <c r="J121" s="3" t="n">
         <v>0</v>
@@ -27132,7 +27132,11 @@
           <t>Acquisition of intangible assets</t>
         </is>
       </c>
-      <c r="D272" t="inlineStr"/>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E272" t="inlineStr">
         <is>
           <t>-</t>
@@ -30082,7 +30086,11 @@
           <t>Reversal of share-based payment expense</t>
         </is>
       </c>
-      <c r="D313" t="inlineStr"/>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E313" t="inlineStr">
         <is>
           <t>-</t>
@@ -31664,7 +31672,11 @@
           <t>Share-based payment expense</t>
         </is>
       </c>
-      <c r="D334" t="inlineStr"/>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E334" t="inlineStr">
         <is>
           <t>-</t>
@@ -32420,7 +32432,11 @@
           <t>Repurchase of common shares</t>
         </is>
       </c>
-      <c r="D344" t="inlineStr"/>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E344" t="inlineStr">
         <is>
           <t>-</t>
@@ -36334,7 +36350,11 @@
           <t>Share-based compensation expense</t>
         </is>
       </c>
-      <c r="D396" t="inlineStr"/>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E396" t="inlineStr">
         <is>
           <t>-</t>
@@ -39102,7 +39122,11 @@
           <t>Share-based compensation expense</t>
         </is>
       </c>
-      <c r="D433" t="inlineStr"/>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E433" t="inlineStr">
         <is>
           <t>-</t>
@@ -40002,7 +40026,11 @@
           <t>Repurchase of shares</t>
         </is>
       </c>
-      <c r="D445" t="inlineStr"/>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E445" t="inlineStr">
         <is>
           <t>-</t>
@@ -44132,7 +44160,11 @@
           <t>Acquisition of intangible assets (16,272)</t>
         </is>
       </c>
-      <c r="D499" t="inlineStr"/>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E499" t="inlineStr">
         <is>
           <t>-</t>
@@ -45742,7 +45774,11 @@
           <t>Change in non-cash operating working capital</t>
         </is>
       </c>
-      <c r="D520" t="inlineStr"/>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E520" s="5" t="n">
         <v>4.966195</v>
       </c>
@@ -45894,7 +45930,11 @@
           <t>Repurchase of shares</t>
         </is>
       </c>
-      <c r="D522" t="inlineStr"/>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E522" s="5" t="n">
         <v>-0.537019</v>
       </c>
@@ -46644,7 +46684,11 @@
           <t>Acquisition of intangible assets</t>
         </is>
       </c>
-      <c r="D532" t="inlineStr"/>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E532" s="5" t="n">
         <v>-0.822581</v>
       </c>
@@ -51192,7 +51236,11 @@
           <t>Share of profit (loss) of associates 22</t>
         </is>
       </c>
-      <c r="D593" t="inlineStr"/>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>EarningsFromEquityInterest</t>
+        </is>
+      </c>
       <c r="E593" t="inlineStr">
         <is>
           <t>-</t>
